--- a/report/股癌_股票追蹤.xlsx
+++ b/report/股癌_股票追蹤.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -673,20 +673,20 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>EP660</t>
+          <t>EP661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>台股42,000點，台積電漲至2,345，估值10-20倍尚未泡沫，仍可持有</t>
+          <t>孟公將部分中小部位轉入台積電，持續持有</t>
         </is>
       </c>
     </row>
@@ -1168,20 +1168,20 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>EP657</t>
+          <t>EP661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>與 MediaTek 同為 OpenAI 手機晶片供應商，每顆 $120 美元</t>
+          <t>近期異軍突起，AIPC故事已死，此次是ASIC/Custom光通晶片/AI Infrastructure敘事</t>
         </is>
       </c>
     </row>
@@ -1933,20 +1933,20 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EP659</t>
+          <t>EP661</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Pierre Chen 開 AI 事實大會大吹猛吹，國巨領頭被動元件全面轉強</t>
+          <t>MLCC 22UF排擠效應受惠，VRubin換代後台系被動元件領頭羊，持續看好</t>
         </is>
       </c>
     </row>
@@ -1978,20 +1978,20 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EP659</t>
+          <t>EP661</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>出貨交期拉長通知，市場給漲停；後續漲價可能性升溫</t>
+          <t>小型MLCC，出貨交期拉長通知，漲價信號前兆</t>
         </is>
       </c>
     </row>
@@ -2158,20 +2158,20 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EP660</t>
+          <t>EP661</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>成熟製程產能賣光，海外客戶願意出溢價搶產能，消費性/成熟製程族群轉強代表</t>
+          <t>成熟製程新加坡廠產能整個被包走，需求驅動型漲價，孟公認為沒有疑問</t>
         </is>
       </c>
     </row>
@@ -2397,6 +2397,231 @@
       <c r="I43" t="inlineStr">
         <is>
           <t>被動元件表現很好，與VSH同步</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>華新科</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>MLCC大廠與國巨並稱被動元件領頭羊，VRubin換代同步受惠</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>鋁電容廠，台系補位日系退場缺口，漲價滲透中</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>8042</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>金山電</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>電容廠，跟上鋁電容漲價趨勢</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Q1毛利改善但股價未反映，防守型低估值候選（古阿康）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>新唐</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>MCU+CPU socket，兩年前Google/微軟綁定故事重新被炒，近期補漲</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4406,6 +4631,326 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>國巨</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>MLCC 22UF排擠效應受惠，VRubin換代後台系被動元件領頭羊，持續看好</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>華新科</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MLCC大廠與國巨並稱被動元件領頭羊，VRubin換代同步受惠</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>信昌電</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>小型MLCC，出貨交期拉長通知，漲價信號前兆</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>鋁電容廠，台系補位日系退場缺口，漲價滲透中</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>8042</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>金山電</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>電容廠，跟上鋁電容漲價趨勢</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>世界先進</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>成熟製程新加坡廠產能整個被包走，需求驅動型漲價，孟公認為沒有疑問</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Q1毛利改善但股價未反映，防守型低估值候選（古阿康）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>高通</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>近期異軍突起，AIPC故事已死，此次是ASIC/Custom光通晶片/AI Infrastructure敘事</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>新唐</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MCU+CPU socket，兩年前Google/微軟綁定故事重新被炒，近期補漲</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EP661</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>孟公將部分中小部位轉入台積電，持續持有</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/股癌_股票追蹤.xlsx
+++ b/report/股癌_股票追蹤.xlsx
@@ -673,20 +673,20 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>EP661</t>
+          <t>EP662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>孟公將部分中小部位轉入台積電，持續持有</t>
+          <t>金管會放寬主動型ETF持股上限，預計1個月後投信陸續增持，籌碼面中期利多；資金輪動可能造成中小股賣壓</t>
         </is>
       </c>
     </row>
@@ -1483,20 +1483,20 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>EP659</t>
+          <t>EP662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>軟體被殺中相對撐得住的標的之一</t>
+          <t>資安股逆勢創新高，Mythos負面衝擊未兌現反而拉升需求，AI時代網路安全支出持續增加</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4951,6 +4951,70 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EP662</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>金管會放寬主動型ETF持股上限，預計1個月後投信陸續增持，籌碼面中期利多；資金輪動可能造成中小股賣壓</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EP662</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>資安股逆勢創新高，Mythos負面衝擊未兌現反而拉升需求，AI時代網路安全支出持續增加</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/股癌_股票追蹤.xlsx
+++ b/report/股癌_股票追蹤.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -673,20 +673,20 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>EP662</t>
+          <t>EP663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>金管會放寬主動型ETF持股上限，預計1個月後投信陸續增持，籌碼面中期利多；資金輪動可能造成中小股賣壓</t>
+          <t>技術論壇揭露三層蛋糕光通架構，確認光通長期方向；有紀律擴產控制保護供需週期</t>
         </is>
       </c>
     </row>
@@ -763,20 +763,20 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>EP660</t>
+          <t>EP663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>連續漲停後進處置，資金面限制引爭議，主持人認為機制應針對大型股調整</t>
+          <t>Broadcom AI晶片V7/V8/V9 Zebrafish系列合作夥伴；某一代代號消失，但供應鏈整體持續，屬老AI族群短期修正中</t>
         </is>
       </c>
     </row>
@@ -2622,6 +2622,51 @@
       <c r="I48" t="inlineStr">
         <is>
           <t>MCU+CPU socket，兩年前Google/微軟綁定故事重新被炒，近期補漲</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EP663</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>EP663</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SoundFish後推出更大顆雙拼版（兩片晶片放在同一載板），老AI短期資金撤退，產品線持續推進；長期故事未結束，等資金輪動回來</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5015,6 +5060,102 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EP663</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>美股</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SoundFish後推出更大顆雙拼版（兩片晶片放在同一載板），老AI短期資金撤退，產品線持續推進；長期故事未結束，等資金輪動回來</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EP663</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Broadcom AI晶片V7/V8/V9 Zebrafish系列合作夥伴；某一代代號消失，但供應鏈整體持續，屬老AI族群短期修正中</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EP663</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>台股</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>技術論壇揭露三層蛋糕光通架構，確認光通長期方向；有紀律擴產控制保護供需週期</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
